--- a/rag/evaluation/multi-hop/system-ledger.xlsx
+++ b/rag/evaluation/multi-hop/system-ledger.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,6 +719,2310 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>SYS-109</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>交通費精算ポータル</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t>交通費 Portal</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>経</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SYS-110</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>勤怠集計システム</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>勤怠集計</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>労</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>SYS-111</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>人事給与システム</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>HRP</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>労</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>SYS-112</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>人材評価分析システム</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>HRA</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SYS-113</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>受注分析システム</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>受注分析</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>業</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>SYS-114</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>発注管理システム</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t>POMS</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>購</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>SYS-115</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>ドキュメント管理システム</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>DMS</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>総</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SYS-116</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>会議室案内システム</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>会議室案内</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>総</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SYS-117</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>資産台帳システム</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>資産台帳</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>財</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>SYS-118</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>予算実績システム</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>予実</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>企</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SYS-119</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>購買管理システム</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>購</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>SYS-120</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>案件管理システム</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t>PMS</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>業</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>SYS-121</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>倉庫管理システム</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t>WMS</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>物</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>SYS-122</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>配送管理システム</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t>TMS</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>物</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>SYS-123</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>生産計画システム</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t>生産計画</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>SYS-124</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>製造実行システム</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>MES</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>SYS-125</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>品質記録システム</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t>QMS</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>品</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>SYS-126</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>検査成績書システム</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>検査成績</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>品</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>SYS-127</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>サプライヤーポータル</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>Supplier Portal</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>購</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>SYS-128</t>
+        </is>
+      </c>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>カスタマーポータル</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>Customer Portal</t>
+        </is>
+      </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>顧</t>
+        </is>
+      </c>
+      <c r="E31" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F31" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>SYS-129</t>
+        </is>
+      </c>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>問い合わせ管理システム</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>顧</t>
+        </is>
+      </c>
+      <c r="E32" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F32" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>SYS-130</t>
+        </is>
+      </c>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>顧客台帳システム</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>顧客台帳</t>
+        </is>
+      </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>業</t>
+        </is>
+      </c>
+      <c r="E33" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F33" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>SYS-131</t>
+        </is>
+      </c>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>契約書管理システム</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>CLM</t>
+        </is>
+      </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>法</t>
+        </is>
+      </c>
+      <c r="E34" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F34" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>SYS-132</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>法令データベース</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="inlineStr">
+        <is>
+          <t>法令DB</t>
+        </is>
+      </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>法</t>
+        </is>
+      </c>
+      <c r="E35" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F35" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>SYS-133</t>
+        </is>
+      </c>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>研究データ管理システム</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="inlineStr">
+        <is>
+          <t>RDM</t>
+        </is>
+      </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>研</t>
+        </is>
+      </c>
+      <c r="E36" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F36" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>SYS-134</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>試作管理システム</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>試作管理</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>研</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>SYS-135</t>
+        </is>
+      </c>
+      <c r="B38" s="1" t="inlineStr">
+        <is>
+          <t>広報素材ライブラリ</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>素材ライブラリ</t>
+        </is>
+      </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>広</t>
+        </is>
+      </c>
+      <c r="E38" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F38" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>SYS-136</t>
+        </is>
+      </c>
+      <c r="B39" s="1" t="inlineStr">
+        <is>
+          <t>社内報配信システム</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>社内報</t>
+        </is>
+      </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>広</t>
+        </is>
+      </c>
+      <c r="E39" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F39" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>SYS-137</t>
+        </is>
+      </c>
+      <c r="B40" s="1" t="inlineStr">
+        <is>
+          <t>監査記録システム</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>監査記録</t>
+        </is>
+      </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>監</t>
+        </is>
+      </c>
+      <c r="E40" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>SYS-138</t>
+        </is>
+      </c>
+      <c r="B41" s="1" t="inlineStr">
+        <is>
+          <t>内部通報窓口システム</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="inlineStr">
+        <is>
+          <t>通報窓口</t>
+        </is>
+      </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>監</t>
+        </is>
+      </c>
+      <c r="E41" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F41" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>SYS-139</t>
+        </is>
+      </c>
+      <c r="B42" s="1" t="inlineStr">
+        <is>
+          <t>ID 管理システム</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="inlineStr">
+        <is>
+          <t>IDM</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>安</t>
+        </is>
+      </c>
+      <c r="E42" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F42" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>SYS-140</t>
+        </is>
+      </c>
+      <c r="B43" s="1" t="inlineStr">
+        <is>
+          <t>ログ監視システム</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="inlineStr">
+        <is>
+          <t>SIEM</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>安</t>
+        </is>
+      </c>
+      <c r="E43" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F43" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>SYS-141</t>
+        </is>
+      </c>
+      <c r="B44" s="1" t="inlineStr">
+        <is>
+          <t>脆弱性管理システム</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>脆弱性管理</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>安</t>
+        </is>
+      </c>
+      <c r="E44" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F44" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SYS-142</t>
+        </is>
+      </c>
+      <c r="B45" s="1" t="inlineStr">
+        <is>
+          <t>資金管理システム</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>TMS</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>財</t>
+        </is>
+      </c>
+      <c r="E45" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F45" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>SYS-143</t>
+        </is>
+      </c>
+      <c r="B46" s="1" t="inlineStr">
+        <is>
+          <t>固定資産システム</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="inlineStr">
+        <is>
+          <t>FAS</t>
+        </is>
+      </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>財</t>
+        </is>
+      </c>
+      <c r="E46" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F46" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>SYS-144</t>
+        </is>
+      </c>
+      <c r="B47" s="1" t="inlineStr">
+        <is>
+          <t>経営ダッシュボード</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>経営DB</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>企</t>
+        </is>
+      </c>
+      <c r="E47" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F47" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>SYS-145</t>
+        </is>
+      </c>
+      <c r="B48" s="1" t="inlineStr">
+        <is>
+          <t>中期計画管理システム</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>中計</t>
+        </is>
+      </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>企</t>
+        </is>
+      </c>
+      <c r="E48" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F48" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>SYS-146</t>
+        </is>
+      </c>
+      <c r="B49" s="1" t="inlineStr">
+        <is>
+          <t>採用管理システム</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="inlineStr">
+        <is>
+          <t>ATS</t>
+        </is>
+      </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E49" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F49" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>SYS-147</t>
+        </is>
+      </c>
+      <c r="B50" s="1" t="inlineStr">
+        <is>
+          <t>研修管理システム</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>LMS</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F50" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>SYS-148</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>健康管理システム</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>健康管理</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>労</t>
+        </is>
+      </c>
+      <c r="E51" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F51" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>SYS-149</t>
+        </is>
+      </c>
+      <c r="B52" s="1" t="inlineStr">
+        <is>
+          <t>社宅管理システム</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="inlineStr">
+        <is>
+          <t>社宅</t>
+        </is>
+      </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>総</t>
+        </is>
+      </c>
+      <c r="E52" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F52" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>SYS-150</t>
+        </is>
+      </c>
+      <c r="B53" s="1" t="inlineStr">
+        <is>
+          <t>文書保管庫システム</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>文書保管庫</t>
+        </is>
+      </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>総</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F53" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>SYS-151</t>
+        </is>
+      </c>
+      <c r="B54" s="1" t="inlineStr">
+        <is>
+          <t>名刺管理システム</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>名刺</t>
+        </is>
+      </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>業</t>
+        </is>
+      </c>
+      <c r="E54" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F54" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>SYS-152</t>
+        </is>
+      </c>
+      <c r="B55" s="1" t="inlineStr">
+        <is>
+          <t>見積管理システム</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="inlineStr">
+        <is>
+          <t>見積</t>
+        </is>
+      </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>業</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F55" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>SYS-153</t>
+        </is>
+      </c>
+      <c r="B56" s="1" t="inlineStr">
+        <is>
+          <t>販売管理システム</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>SMS</t>
+        </is>
+      </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>営</t>
+        </is>
+      </c>
+      <c r="E56" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F56" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>SYS-154</t>
+        </is>
+      </c>
+      <c r="B57" s="1" t="inlineStr">
+        <is>
+          <t>販売分析システム</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>販売分析</t>
+        </is>
+      </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>営</t>
+        </is>
+      </c>
+      <c r="E57" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F57" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>SYS-155</t>
+        </is>
+      </c>
+      <c r="B58" s="1" t="inlineStr">
+        <is>
+          <t>請求書発行システム</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>請求書</t>
+        </is>
+      </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>経</t>
+        </is>
+      </c>
+      <c r="E58" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F58" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>SYS-156</t>
+        </is>
+      </c>
+      <c r="B59" s="1" t="inlineStr">
+        <is>
+          <t>支払管理システム</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>支払</t>
+        </is>
+      </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>経</t>
+        </is>
+      </c>
+      <c r="E59" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F59" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>SYS-157</t>
+        </is>
+      </c>
+      <c r="B60" s="1" t="inlineStr">
+        <is>
+          <t>会計システム</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="inlineStr">
+        <is>
+          <t>GL</t>
+        </is>
+      </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>経</t>
+        </is>
+      </c>
+      <c r="E60" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F60" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>SYS-158</t>
+        </is>
+      </c>
+      <c r="B61" s="1" t="inlineStr">
+        <is>
+          <t>連結会計システム</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>連結</t>
+        </is>
+      </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>財</t>
+        </is>
+      </c>
+      <c r="E61" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F61" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>SYS-159</t>
+        </is>
+      </c>
+      <c r="B62" s="1" t="inlineStr">
+        <is>
+          <t>在庫管理システム</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>物</t>
+        </is>
+      </c>
+      <c r="E62" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F62" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>SYS-160</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
+        <is>
+          <t>入出荷管理システム</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="inlineStr">
+        <is>
+          <t>入出荷</t>
+        </is>
+      </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>物</t>
+        </is>
+      </c>
+      <c r="E63" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F63" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>SYS-161</t>
+        </is>
+      </c>
+      <c r="B64" s="1" t="inlineStr">
+        <is>
+          <t>設備保全システム</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="inlineStr">
+        <is>
+          <t>設備保全</t>
+        </is>
+      </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F64" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
+        <is>
+          <t>SYS-162</t>
+        </is>
+      </c>
+      <c r="B65" s="1" t="inlineStr">
+        <is>
+          <t>工程管理システム</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>工程管理</t>
+        </is>
+      </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>製</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F65" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
+        <is>
+          <t>SYS-163</t>
+        </is>
+      </c>
+      <c r="B66" s="1" t="inlineStr">
+        <is>
+          <t>図面管理システム</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>PDM</t>
+        </is>
+      </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>研</t>
+        </is>
+      </c>
+      <c r="E66" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F66" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>SYS-164</t>
+        </is>
+      </c>
+      <c r="B67" s="1" t="inlineStr">
+        <is>
+          <t>特許管理システム</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="inlineStr">
+        <is>
+          <t>特許</t>
+        </is>
+      </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>法</t>
+        </is>
+      </c>
+      <c r="E67" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F67" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
+        <is>
+          <t>SYS-165</t>
+        </is>
+      </c>
+      <c r="B68" s="1" t="inlineStr">
+        <is>
+          <t>取引先審査システム</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>与信</t>
+        </is>
+      </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>財</t>
+        </is>
+      </c>
+      <c r="E68" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F68" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="inlineStr">
+        <is>
+          <t>SYS-166</t>
+        </is>
+      </c>
+      <c r="B69" s="1" t="inlineStr">
+        <is>
+          <t>電子契約システム</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>電子契約</t>
+        </is>
+      </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>法</t>
+        </is>
+      </c>
+      <c r="E69" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F69" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="inlineStr">
+        <is>
+          <t>SYS-167</t>
+        </is>
+      </c>
+      <c r="B70" s="1" t="inlineStr">
+        <is>
+          <t>受付管理システム</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>受付</t>
+        </is>
+      </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>総</t>
+        </is>
+      </c>
+      <c r="E70" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F70" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
+        <is>
+          <t>SYS-168</t>
+        </is>
+      </c>
+      <c r="B71" s="1" t="inlineStr">
+        <is>
+          <t>備品予約システム</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>備品予約</t>
+        </is>
+      </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>総</t>
+        </is>
+      </c>
+      <c r="E71" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F71" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
+        <is>
+          <t>SYS-169</t>
+        </is>
+      </c>
+      <c r="B72" s="1" t="inlineStr">
+        <is>
+          <t>アンケート集計システム</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="inlineStr">
+        <is>
+          <t>アンケート</t>
+        </is>
+      </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>広</t>
+        </is>
+      </c>
+      <c r="E72" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F72" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
+        <is>
+          <t>SYS-170</t>
+        </is>
+      </c>
+      <c r="B73" s="1" t="inlineStr">
+        <is>
+          <t>ウェブサイト管理システム</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="inlineStr">
+        <is>
+          <t>CMS</t>
+        </is>
+      </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>広</t>
+        </is>
+      </c>
+      <c r="E73" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F73" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
+        <is>
+          <t>SYS-171</t>
+        </is>
+      </c>
+      <c r="B74" s="1" t="inlineStr">
+        <is>
+          <t>コールセンターシステム</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>CTI</t>
+        </is>
+      </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>顧</t>
+        </is>
+      </c>
+      <c r="E74" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
+        <is>
+          <t>SYS-172</t>
+        </is>
+      </c>
+      <c r="B75" s="1" t="inlineStr">
+        <is>
+          <t>FAQ 管理システム</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>FAQ</t>
+        </is>
+      </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>顧</t>
+        </is>
+      </c>
+      <c r="E75" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F75" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
+        <is>
+          <t>SYS-173</t>
+        </is>
+      </c>
+      <c r="B76" s="1" t="inlineStr">
+        <is>
+          <t>返品管理システム</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="inlineStr">
+        <is>
+          <t>返品</t>
+        </is>
+      </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>顧</t>
+        </is>
+      </c>
+      <c r="E76" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F76" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="inlineStr">
+        <is>
+          <t>SYS-174</t>
+        </is>
+      </c>
+      <c r="B77" s="1" t="inlineStr">
+        <is>
+          <t>輸出管理システム</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>輸出管理</t>
+        </is>
+      </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>法</t>
+        </is>
+      </c>
+      <c r="E77" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F77" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>SYS-175</t>
+        </is>
+      </c>
+      <c r="B78" s="1" t="inlineStr">
+        <is>
+          <t>原価管理システム</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>原価</t>
+        </is>
+      </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>経</t>
+        </is>
+      </c>
+      <c r="E78" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F78" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
+        <is>
+          <t>SYS-176</t>
+        </is>
+      </c>
+      <c r="B79" s="1" t="inlineStr">
+        <is>
+          <t>経費分析システム</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="inlineStr">
+        <is>
+          <t>経費分析</t>
+        </is>
+      </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>企</t>
+        </is>
+      </c>
+      <c r="E79" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F79" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
+        <is>
+          <t>SYS-177</t>
+        </is>
+      </c>
+      <c r="B80" s="1" t="inlineStr">
+        <is>
+          <t>稟議システム</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="inlineStr">
+        <is>
+          <t>稟議</t>
+        </is>
+      </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>総</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
+        <is>
+          <t>SYS-178</t>
+        </is>
+      </c>
+      <c r="B81" s="1" t="inlineStr">
+        <is>
+          <t>監査調書システム</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>調書</t>
+        </is>
+      </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>監</t>
+        </is>
+      </c>
+      <c r="E81" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F81" s="1" t="inlineStr">
+        <is>
+          <t>極秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
+        <is>
+          <t>SYS-179</t>
+        </is>
+      </c>
+      <c r="B82" s="1" t="inlineStr">
+        <is>
+          <t>端末管理システム</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>MDM</t>
+        </is>
+      </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>安</t>
+        </is>
+      </c>
+      <c r="E82" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F82" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
+        <is>
+          <t>SYS-180</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>勤務シフト管理システム</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>シフト</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>労</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>社内限り</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/rag/evaluation/multi-hop/system-ledger.xlsx
+++ b/rag/evaluation/multi-hop/system-ledger.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,86 +434,61 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>重要度は A・B・C の 3 段階です。A が最も高く、B、C の順に低くなります。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>システムID</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>正式名</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>略称・別表記</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>担当部署</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>重要度</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>機密区分</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>SYS-101</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>経費精算ポータル</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>経費 Portal</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>経</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SYS-102</t>
+          <t>SYS-101</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>勤怠管理システム</t>
+          <t>経費精算ポータル</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>勤怠</t>
+          <t>経費 Portal</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
-          <t>人</t>
+          <t>経</t>
         </is>
       </c>
       <c r="E5" s="1" t="inlineStr">
@@ -530,17 +505,17 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SYS-103</t>
+          <t>SYS-102</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>人事評価システム</t>
+          <t>勤怠管理システム</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>HRM</t>
+          <t>勤怠</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -550,34 +525,34 @@
       </c>
       <c r="E6" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SYS-104</t>
+          <t>SYS-103</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>受発注管理システム</t>
+          <t>人事評価システム</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>OMS、受発注</t>
+          <t>HRM</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>営</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -587,56 +562,56 @@
       </c>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SYS-105</t>
+          <t>SYS-104</t>
         </is>
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>ドキュメントポータル</t>
+          <t>受発注管理システム</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Document Portal</t>
+          <t>OMS、受発注</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>総</t>
+          <t>営</t>
         </is>
       </c>
       <c r="E8" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F8" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SYS-106</t>
+          <t>SYS-105</t>
         </is>
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
-          <t>会議室予約システム</t>
+          <t>ドキュメントポータル</t>
         </is>
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>会議室予約</t>
+          <t>Document Portal</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -646,7 +621,7 @@
       </c>
       <c r="E9" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F9" s="1" t="inlineStr">
@@ -658,81 +633,81 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>SYS-107</t>
+          <t>SYS-106</t>
         </is>
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>資産管理システム</t>
+          <t>会議室予約システム</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>会議室予約</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>情</t>
+          <t>総</t>
         </is>
       </c>
       <c r="E10" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SYS-108</t>
+          <t>SYS-107</t>
         </is>
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
-          <t>予算管理システム</t>
+          <t>資産管理システム</t>
         </is>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>経</t>
+          <t>情</t>
         </is>
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>SYS-109</t>
+          <t>SYS-108</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>交通費精算ポータル</t>
+          <t>予算管理システム</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>交通費 Portal</t>
+          <t>BMS</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
@@ -742,39 +717,39 @@
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F12" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SYS-110</t>
+          <t>SYS-109</t>
         </is>
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>勤怠集計システム</t>
+          <t>交通費精算ポータル</t>
         </is>
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>勤怠集計</t>
+          <t>交通費 Portal</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
-          <t>労</t>
+          <t>経</t>
         </is>
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F13" s="1" t="inlineStr">
@@ -786,17 +761,17 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SYS-111</t>
+          <t>SYS-110</t>
         </is>
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>人事給与システム</t>
+          <t>勤怠集計システム</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>HRP</t>
+          <t>勤怠集計</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -806,7 +781,7 @@
       </c>
       <c r="E14" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F14" s="1" t="inlineStr">
@@ -818,54 +793,54 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>SYS-112</t>
+          <t>SYS-111</t>
         </is>
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>人材評価分析システム</t>
+          <t>人事給与システム</t>
         </is>
       </c>
       <c r="C15" s="1" t="inlineStr">
         <is>
-          <t>HRA</t>
+          <t>HRP</t>
         </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>人</t>
+          <t>労</t>
         </is>
       </c>
       <c r="E15" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F15" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>SYS-113</t>
+          <t>SYS-112</t>
         </is>
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>受注分析システム</t>
+          <t>人材評価分析システム</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
         <is>
-          <t>受注分析</t>
+          <t>HRA</t>
         </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>業</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E16" s="1" t="inlineStr">
@@ -875,34 +850,34 @@
       </c>
       <c r="F16" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>SYS-114</t>
+          <t>SYS-113</t>
         </is>
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>発注管理システム</t>
+          <t>受注分析システム</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>POMS</t>
+          <t>受注分析</t>
         </is>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>購</t>
+          <t>業</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F17" s="1" t="inlineStr">
@@ -914,49 +889,49 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>SYS-115</t>
+          <t>SYS-114</t>
         </is>
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>ドキュメント管理システム</t>
+          <t>発注管理システム</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>DMS</t>
+          <t>POMS</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>総</t>
+          <t>購</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F18" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>SYS-116</t>
+          <t>SYS-115</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>会議室案内システム</t>
+          <t>ドキュメント管理システム</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>会議室案内</t>
+          <t>DMS</t>
         </is>
       </c>
       <c r="D19" s="1" t="inlineStr">
@@ -966,7 +941,7 @@
       </c>
       <c r="E19" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F19" s="1" t="inlineStr">
@@ -978,54 +953,54 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SYS-117</t>
+          <t>SYS-116</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>資産台帳システム</t>
+          <t>会議室案内システム</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>資産台帳</t>
+          <t>会議室案内</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>財</t>
+          <t>総</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F20" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>SYS-118</t>
+          <t>SYS-117</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>予算実績システム</t>
+          <t>資産台帳システム</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>予実</t>
+          <t>資産台帳</t>
         </is>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>企</t>
+          <t>財</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -1035,51 +1010,51 @@
       </c>
       <c r="F21" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SYS-119</t>
+          <t>SYS-118</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>購買管理システム</t>
+          <t>予算実績システム</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>PMS</t>
+          <t>予実</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>購</t>
+          <t>企</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F22" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>SYS-120</t>
+          <t>SYS-119</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>案件管理システム</t>
+          <t>購買管理システム</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1089,12 +1064,12 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>業</t>
+          <t>購</t>
         </is>
       </c>
       <c r="E23" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F23" s="1" t="inlineStr">
@@ -1106,27 +1081,27 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>SYS-121</t>
+          <t>SYS-120</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>倉庫管理システム</t>
+          <t>案件管理システム</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>WMS</t>
+          <t>PMS</t>
         </is>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>物</t>
+          <t>業</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F24" s="1" t="inlineStr">
@@ -1138,17 +1113,17 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>SYS-122</t>
+          <t>SYS-121</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>配送管理システム</t>
+          <t>倉庫管理システム</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>WMS</t>
         </is>
       </c>
       <c r="D25" s="1" t="inlineStr">
@@ -1158,61 +1133,61 @@
       </c>
       <c r="E25" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F25" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>SYS-123</t>
+          <t>SYS-122</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>生産計画システム</t>
+          <t>配送管理システム</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
-          <t>生産計画</t>
+          <t>TMS</t>
         </is>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>製</t>
+          <t>物</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>SYS-124</t>
+          <t>SYS-123</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>製造実行システム</t>
+          <t>生産計画システム</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
         <is>
-          <t>MES</t>
+          <t>生産計画</t>
         </is>
       </c>
       <c r="D27" s="1" t="inlineStr">
@@ -1234,22 +1209,22 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>SYS-125</t>
+          <t>SYS-124</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>品質記録システム</t>
+          <t>製造実行システム</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>QMS</t>
+          <t>MES</t>
         </is>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>品</t>
+          <t>製</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1266,17 +1241,17 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>SYS-126</t>
+          <t>SYS-125</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>検査成績書システム</t>
+          <t>品質記録システム</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
         <is>
-          <t>検査成績</t>
+          <t>QMS</t>
         </is>
       </c>
       <c r="D29" s="1" t="inlineStr">
@@ -1286,7 +1261,7 @@
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F29" s="1" t="inlineStr">
@@ -1298,22 +1273,22 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>SYS-127</t>
+          <t>SYS-126</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>サプライヤーポータル</t>
+          <t>検査成績書システム</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
-          <t>Supplier Portal</t>
+          <t>検査成績</t>
         </is>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
-          <t>購</t>
+          <t>品</t>
         </is>
       </c>
       <c r="E30" s="1" t="inlineStr">
@@ -1330,27 +1305,27 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>SYS-128</t>
+          <t>SYS-127</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>カスタマーポータル</t>
+          <t>サプライヤーポータル</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
         <is>
-          <t>Customer Portal</t>
+          <t>Supplier Portal</t>
         </is>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>顧</t>
+          <t>購</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F31" s="1" t="inlineStr">
@@ -1362,17 +1337,17 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>SYS-129</t>
+          <t>SYS-128</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>問い合わせ管理システム</t>
+          <t>カスタマーポータル</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>Customer Portal</t>
         </is>
       </c>
       <c r="D32" s="1" t="inlineStr">
@@ -1382,34 +1357,34 @@
       </c>
       <c r="E32" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F32" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>SYS-130</t>
+          <t>SYS-129</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>顧客台帳システム</t>
+          <t>問い合わせ管理システム</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
         <is>
-          <t>顧客台帳</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="D33" s="1" t="inlineStr">
         <is>
-          <t>業</t>
+          <t>顧</t>
         </is>
       </c>
       <c r="E33" s="1" t="inlineStr">
@@ -1426,22 +1401,22 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>SYS-131</t>
+          <t>SYS-130</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>契約書管理システム</t>
+          <t>顧客台帳システム</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
         <is>
-          <t>CLM</t>
+          <t>顧客台帳</t>
         </is>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>法</t>
+          <t>業</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1458,17 +1433,17 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SYS-132</t>
+          <t>SYS-131</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>法令データベース</t>
+          <t>契約書管理システム</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
         <is>
-          <t>法令DB</t>
+          <t>CLM</t>
         </is>
       </c>
       <c r="D35" s="1" t="inlineStr">
@@ -1478,61 +1453,61 @@
       </c>
       <c r="E35" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F35" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>SYS-133</t>
+          <t>SYS-132</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>研究データ管理システム</t>
+          <t>法令データベース</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
         <is>
-          <t>RDM</t>
+          <t>法令DB</t>
         </is>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
-          <t>研</t>
+          <t>法</t>
         </is>
       </c>
       <c r="E36" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F36" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>SYS-134</t>
+          <t>SYS-133</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>試作管理システム</t>
+          <t>研究データ管理システム</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
         <is>
-          <t>試作管理</t>
+          <t>RDM</t>
         </is>
       </c>
       <c r="D37" s="1" t="inlineStr">
@@ -1542,34 +1517,34 @@
       </c>
       <c r="E37" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F37" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>SYS-135</t>
+          <t>SYS-134</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>広報素材ライブラリ</t>
+          <t>試作管理システム</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>素材ライブラリ</t>
+          <t>試作管理</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>広</t>
+          <t>研</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
@@ -1579,24 +1554,24 @@
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>SYS-136</t>
+          <t>SYS-135</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>社内報配信システム</t>
+          <t>広報素材ライブラリ</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
         <is>
-          <t>社内報</t>
+          <t>素材ライブラリ</t>
         </is>
       </c>
       <c r="D39" s="1" t="inlineStr">
@@ -1618,49 +1593,49 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>SYS-137</t>
+          <t>SYS-136</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>監査記録システム</t>
+          <t>社内報配信システム</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
         <is>
-          <t>監査記録</t>
+          <t>社内報</t>
         </is>
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>監</t>
+          <t>広</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F40" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>SYS-138</t>
+          <t>SYS-137</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>内部通報窓口システム</t>
+          <t>監査記録システム</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>通報窓口</t>
+          <t>監査記録</t>
         </is>
       </c>
       <c r="D41" s="1" t="inlineStr">
@@ -1682,49 +1657,49 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>SYS-139</t>
+          <t>SYS-138</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>ID 管理システム</t>
+          <t>内部通報窓口システム</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>IDM</t>
+          <t>通報窓口</t>
         </is>
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>安</t>
+          <t>監</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F42" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>SYS-140</t>
+          <t>SYS-139</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>ログ監視システム</t>
+          <t>ID 管理システム</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
         <is>
-          <t>SIEM</t>
+          <t>IDM</t>
         </is>
       </c>
       <c r="D43" s="1" t="inlineStr">
@@ -1746,17 +1721,17 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>SYS-141</t>
+          <t>SYS-140</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>脆弱性管理システム</t>
+          <t>ログ監視システム</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
         <is>
-          <t>脆弱性管理</t>
+          <t>SIEM</t>
         </is>
       </c>
       <c r="D44" s="1" t="inlineStr">
@@ -1766,7 +1741,7 @@
       </c>
       <c r="E44" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F44" s="1" t="inlineStr">
@@ -1778,27 +1753,27 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>SYS-142</t>
+          <t>SYS-141</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>資金管理システム</t>
+          <t>脆弱性管理システム</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
         <is>
-          <t>TMS</t>
+          <t>脆弱性管理</t>
         </is>
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>財</t>
+          <t>安</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F45" s="1" t="inlineStr">
@@ -1810,17 +1785,17 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>SYS-143</t>
+          <t>SYS-142</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>固定資産システム</t>
+          <t>資金管理システム</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>FAS</t>
+          <t>TMS</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
@@ -1830,7 +1805,7 @@
       </c>
       <c r="E46" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F46" s="1" t="inlineStr">
@@ -1842,22 +1817,22 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>SYS-144</t>
+          <t>SYS-143</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>経営ダッシュボード</t>
+          <t>固定資産システム</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>経営DB</t>
+          <t>FAS</t>
         </is>
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>企</t>
+          <t>財</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1867,24 +1842,24 @@
       </c>
       <c r="F47" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>SYS-145</t>
+          <t>SYS-144</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>中期計画管理システム</t>
+          <t>経営ダッシュボード</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>中計</t>
+          <t>経営DB</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
@@ -1894,7 +1869,7 @@
       </c>
       <c r="E48" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F48" s="1" t="inlineStr">
@@ -1906,27 +1881,27 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>SYS-146</t>
+          <t>SYS-145</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>採用管理システム</t>
+          <t>中期計画管理システム</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
         <is>
-          <t>ATS</t>
+          <t>中計</t>
         </is>
       </c>
       <c r="D49" s="1" t="inlineStr">
         <is>
-          <t>人</t>
+          <t>企</t>
         </is>
       </c>
       <c r="E49" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F49" s="1" t="inlineStr">
@@ -1938,17 +1913,17 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>SYS-147</t>
+          <t>SYS-146</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>研修管理システム</t>
+          <t>採用管理システム</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>LMS</t>
+          <t>ATS</t>
         </is>
       </c>
       <c r="D50" s="1" t="inlineStr">
@@ -1958,93 +1933,93 @@
       </c>
       <c r="E50" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F50" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>SYS-148</t>
+          <t>SYS-147</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>健康管理システム</t>
+          <t>研修管理システム</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>健康管理</t>
+          <t>LMS</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>労</t>
+          <t>人</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F51" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>SYS-149</t>
+          <t>SYS-148</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>社宅管理システム</t>
+          <t>健康管理システム</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
-          <t>社宅</t>
+          <t>健康管理</t>
         </is>
       </c>
       <c r="D52" s="1" t="inlineStr">
         <is>
-          <t>総</t>
+          <t>労</t>
         </is>
       </c>
       <c r="E52" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F52" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>SYS-150</t>
+          <t>SYS-149</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>文書保管庫システム</t>
+          <t>社宅管理システム</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
-          <t>文書保管庫</t>
+          <t>社宅</t>
         </is>
       </c>
       <c r="D53" s="1" t="inlineStr">
@@ -2054,7 +2029,7 @@
       </c>
       <c r="E53" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F53" s="1" t="inlineStr">
@@ -2066,27 +2041,27 @@
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>SYS-151</t>
+          <t>SYS-150</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>名刺管理システム</t>
+          <t>文書保管庫システム</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
         <is>
-          <t>名刺</t>
+          <t>文書保管庫</t>
         </is>
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>業</t>
+          <t>総</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F54" s="1" t="inlineStr">
@@ -2098,17 +2073,17 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>SYS-152</t>
+          <t>SYS-151</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>見積管理システム</t>
+          <t>名刺管理システム</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
-          <t>見積</t>
+          <t>名刺</t>
         </is>
       </c>
       <c r="D55" s="1" t="inlineStr">
@@ -2118,7 +2093,7 @@
       </c>
       <c r="E55" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F55" s="1" t="inlineStr">
@@ -2130,27 +2105,27 @@
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>SYS-153</t>
+          <t>SYS-152</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>販売管理システム</t>
+          <t>見積管理システム</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>SMS</t>
+          <t>見積</t>
         </is>
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>営</t>
+          <t>業</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F56" s="1" t="inlineStr">
@@ -2162,17 +2137,17 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>SYS-154</t>
+          <t>SYS-153</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>販売分析システム</t>
+          <t>販売管理システム</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
         <is>
-          <t>販売分析</t>
+          <t>SMS</t>
         </is>
       </c>
       <c r="D57" s="1" t="inlineStr">
@@ -2182,7 +2157,7 @@
       </c>
       <c r="E57" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F57" s="1" t="inlineStr">
@@ -2194,27 +2169,27 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>SYS-155</t>
+          <t>SYS-154</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>請求書発行システム</t>
+          <t>販売分析システム</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>請求書</t>
+          <t>販売分析</t>
         </is>
       </c>
       <c r="D58" s="1" t="inlineStr">
         <is>
-          <t>経</t>
+          <t>営</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F58" s="1" t="inlineStr">
@@ -2226,17 +2201,17 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>SYS-156</t>
+          <t>SYS-155</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>支払管理システム</t>
+          <t>請求書発行システム</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
         <is>
-          <t>支払</t>
+          <t>請求書</t>
         </is>
       </c>
       <c r="D59" s="1" t="inlineStr">
@@ -2246,7 +2221,7 @@
       </c>
       <c r="E59" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F59" s="1" t="inlineStr">
@@ -2258,17 +2233,17 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>SYS-157</t>
+          <t>SYS-156</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>会計システム</t>
+          <t>支払管理システム</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
         <is>
-          <t>GL</t>
+          <t>支払</t>
         </is>
       </c>
       <c r="D60" s="1" t="inlineStr">
@@ -2278,7 +2253,7 @@
       </c>
       <c r="E60" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F60" s="1" t="inlineStr">
@@ -2290,81 +2265,81 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>SYS-158</t>
+          <t>SYS-157</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>連結会計システム</t>
+          <t>会計システム</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
         <is>
-          <t>連結</t>
+          <t>GL</t>
         </is>
       </c>
       <c r="D61" s="1" t="inlineStr">
         <is>
-          <t>財</t>
+          <t>経</t>
         </is>
       </c>
       <c r="E61" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F61" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>SYS-159</t>
+          <t>SYS-158</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>在庫管理システム</t>
+          <t>連結会計システム</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
         <is>
-          <t>IMS</t>
+          <t>連結</t>
         </is>
       </c>
       <c r="D62" s="1" t="inlineStr">
         <is>
-          <t>物</t>
+          <t>財</t>
         </is>
       </c>
       <c r="E62" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F62" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>SYS-160</t>
+          <t>SYS-159</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>入出荷管理システム</t>
+          <t>在庫管理システム</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
         <is>
-          <t>入出荷</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D63" s="1" t="inlineStr">
@@ -2374,34 +2349,34 @@
       </c>
       <c r="E63" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F63" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>SYS-161</t>
+          <t>SYS-160</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>設備保全システム</t>
+          <t>入出荷管理システム</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
-          <t>設備保全</t>
+          <t>入出荷</t>
         </is>
       </c>
       <c r="D64" s="1" t="inlineStr">
         <is>
-          <t>製</t>
+          <t>物</t>
         </is>
       </c>
       <c r="E64" s="1" t="inlineStr">
@@ -2418,17 +2393,17 @@
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>SYS-162</t>
+          <t>SYS-161</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>工程管理システム</t>
+          <t>設備保全システム</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
-          <t>工程管理</t>
+          <t>設備保全</t>
         </is>
       </c>
       <c r="D65" s="1" t="inlineStr">
@@ -2443,29 +2418,29 @@
       </c>
       <c r="F65" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>SYS-163</t>
+          <t>SYS-162</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>図面管理システム</t>
+          <t>工程管理システム</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
-          <t>PDM</t>
+          <t>工程管理</t>
         </is>
       </c>
       <c r="D66" s="1" t="inlineStr">
         <is>
-          <t>研</t>
+          <t>製</t>
         </is>
       </c>
       <c r="E66" s="1" t="inlineStr">
@@ -2475,34 +2450,34 @@
       </c>
       <c r="F66" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>SYS-164</t>
+          <t>SYS-163</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>特許管理システム</t>
+          <t>図面管理システム</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>特許</t>
+          <t>PDM</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
-          <t>法</t>
+          <t>研</t>
         </is>
       </c>
       <c r="E67" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F67" s="1" t="inlineStr">
@@ -2514,27 +2489,27 @@
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>SYS-165</t>
+          <t>SYS-164</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>取引先審査システム</t>
+          <t>特許管理システム</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>与信</t>
+          <t>特許</t>
         </is>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
-          <t>財</t>
+          <t>法</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F68" s="1" t="inlineStr">
@@ -2546,22 +2521,22 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>SYS-166</t>
+          <t>SYS-165</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>電子契約システム</t>
+          <t>取引先審査システム</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
         <is>
-          <t>電子契約</t>
+          <t>与信</t>
         </is>
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>法</t>
+          <t>財</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -2571,56 +2546,56 @@
       </c>
       <c r="F69" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>SYS-167</t>
+          <t>SYS-166</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>受付管理システム</t>
+          <t>電子契約システム</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
         <is>
-          <t>受付</t>
+          <t>電子契約</t>
         </is>
       </c>
       <c r="D70" s="1" t="inlineStr">
         <is>
-          <t>総</t>
+          <t>法</t>
         </is>
       </c>
       <c r="E70" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F70" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>SYS-168</t>
+          <t>SYS-167</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>備品予約システム</t>
+          <t>受付管理システム</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
         <is>
-          <t>備品予約</t>
+          <t>受付</t>
         </is>
       </c>
       <c r="D71" s="1" t="inlineStr">
@@ -2642,22 +2617,22 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>SYS-169</t>
+          <t>SYS-168</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>アンケート集計システム</t>
+          <t>備品予約システム</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
         <is>
-          <t>アンケート</t>
+          <t>備品予約</t>
         </is>
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>広</t>
+          <t>総</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2674,17 +2649,17 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>SYS-170</t>
+          <t>SYS-169</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>ウェブサイト管理システム</t>
+          <t>アンケート集計システム</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
         <is>
-          <t>CMS</t>
+          <t>アンケート</t>
         </is>
       </c>
       <c r="D73" s="1" t="inlineStr">
@@ -2694,7 +2669,7 @@
       </c>
       <c r="E73" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F73" s="1" t="inlineStr">
@@ -2706,49 +2681,49 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>SYS-171</t>
+          <t>SYS-170</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>コールセンターシステム</t>
+          <t>ウェブサイト管理システム</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
         <is>
-          <t>CTI</t>
+          <t>CMS</t>
         </is>
       </c>
       <c r="D74" s="1" t="inlineStr">
         <is>
-          <t>顧</t>
+          <t>広</t>
         </is>
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F74" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>SYS-172</t>
+          <t>SYS-171</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>FAQ 管理システム</t>
+          <t>コールセンターシステム</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
         <is>
-          <t>FAQ</t>
+          <t>CTI</t>
         </is>
       </c>
       <c r="D75" s="1" t="inlineStr">
@@ -2758,29 +2733,29 @@
       </c>
       <c r="E75" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F75" s="1" t="inlineStr">
         <is>
-          <t>社内限り</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>SYS-173</t>
+          <t>SYS-172</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>返品管理システム</t>
+          <t>FAQ 管理システム</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
         <is>
-          <t>返品</t>
+          <t>FAQ</t>
         </is>
       </c>
       <c r="D76" s="1" t="inlineStr">
@@ -2790,34 +2765,34 @@
       </c>
       <c r="E76" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F76" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>社内限り</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>SYS-174</t>
+          <t>SYS-173</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>輸出管理システム</t>
+          <t>返品管理システム</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
         <is>
-          <t>輸出管理</t>
+          <t>返品</t>
         </is>
       </c>
       <c r="D77" s="1" t="inlineStr">
         <is>
-          <t>法</t>
+          <t>顧</t>
         </is>
       </c>
       <c r="E77" s="1" t="inlineStr">
@@ -2834,22 +2809,22 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>SYS-175</t>
+          <t>SYS-174</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>原価管理システム</t>
+          <t>輸出管理システム</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
         <is>
-          <t>原価</t>
+          <t>輸出管理</t>
         </is>
       </c>
       <c r="D78" s="1" t="inlineStr">
         <is>
-          <t>経</t>
+          <t>法</t>
         </is>
       </c>
       <c r="E78" s="1" t="inlineStr">
@@ -2859,66 +2834,66 @@
       </c>
       <c r="F78" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>SYS-176</t>
+          <t>SYS-175</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>経費分析システム</t>
+          <t>原価管理システム</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
         <is>
-          <t>経費分析</t>
+          <t>原価</t>
         </is>
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>企</t>
+          <t>経</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="F79" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>SYS-177</t>
+          <t>SYS-176</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>稟議システム</t>
+          <t>経費分析システム</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
         <is>
-          <t>稟議</t>
+          <t>経費分析</t>
         </is>
       </c>
       <c r="D80" s="1" t="inlineStr">
         <is>
-          <t>総</t>
+          <t>企</t>
         </is>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F80" s="1" t="inlineStr">
@@ -2930,94 +2905,126 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>SYS-178</t>
+          <t>SYS-177</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>監査調書システム</t>
+          <t>稟議システム</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
         <is>
-          <t>調書</t>
+          <t>稟議</t>
         </is>
       </c>
       <c r="D81" s="1" t="inlineStr">
         <is>
-          <t>監</t>
+          <t>総</t>
         </is>
       </c>
       <c r="E81" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="F81" s="1" t="inlineStr">
         <is>
-          <t>極秘</t>
+          <t>社外秘</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>SYS-179</t>
+          <t>SYS-178</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>端末管理システム</t>
+          <t>監査調書システム</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
         <is>
-          <t>MDM</t>
+          <t>調書</t>
         </is>
       </c>
       <c r="D82" s="1" t="inlineStr">
         <is>
-          <t>安</t>
+          <t>監</t>
         </is>
       </c>
       <c r="E82" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="F82" s="1" t="inlineStr">
         <is>
-          <t>社外秘</t>
+          <t>極秘</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
+          <t>SYS-179</t>
+        </is>
+      </c>
+      <c r="B83" s="1" t="inlineStr">
+        <is>
+          <t>端末管理システム</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>MDM</t>
+        </is>
+      </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>安</t>
+        </is>
+      </c>
+      <c r="E83" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F83" s="1" t="inlineStr">
+        <is>
+          <t>社外秘</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="inlineStr">
+        <is>
           <t>SYS-180</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
+      <c r="B84" s="1" t="inlineStr">
         <is>
           <t>勤務シフト管理システム</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
+      <c r="C84" s="1" t="inlineStr">
         <is>
           <t>シフト</t>
         </is>
       </c>
-      <c r="D83" s="1" t="inlineStr">
+      <c r="D84" s="1" t="inlineStr">
         <is>
           <t>労</t>
         </is>
       </c>
-      <c r="E83" s="1" t="inlineStr">
+      <c r="E84" s="1" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="F83" s="1" t="inlineStr">
+      <c r="F84" s="1" t="inlineStr">
         <is>
           <t>社内限り</t>
         </is>
